--- a/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
+++ b/InputData/trans/SRPbVT/Separately Regulated Pollutants by Vehicle Type.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\SRPbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganM\Documents\eps-us\InputData\trans\SRPbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -208,7 +208,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +220,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -248,18 +256,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -539,17 +550,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="101.140625" customWidth="1"/>
+    <col min="2" max="2" width="101.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -557,234 +568,237 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B17" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <v>2009</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B26" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -794,12 +808,12 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -840,7 +854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -881,7 +895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -922,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -963,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -983,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1004,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -1024,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1045,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -1092,31 +1106,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1124,24 +1139,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1160,70 +1236,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1334,23 +1363,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501A1D5E-E6D9-4982-A1CB-AE24D8240A68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8805EA-4D04-4DBD-8151-CE834E217A0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E30F486-1080-4C60-A5FF-51577973276E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F04457EB-C290-4494-9FC6-EFE7D1BBE071}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C25EC3E-3B14-437D-9835-5A2FC4AB70B4}"/>
 </file>